--- a/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2784.32</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5568.63</v>
+        <v>5391.07</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80533.59</v>
+        <v>77965.63</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>85951.87</v>
+        <v>83211.14</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2338.83</v>
+        <v>2264.25</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13364.72</v>
+        <v>12938.56</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5568.63</v>
+        <v>5391.07</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38579.5</v>
+        <v>37349.32</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7486.83</v>
+        <v>7248.1</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2335.49</v>
+        <v>2261.01</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>35639.26</v>
+        <v>34502.84</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2338.83</v>
+        <v>2264.25</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8909.82</v>
+        <v>8625.709999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2335.49</v>
+        <v>2261.01</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4454.91</v>
+        <v>4312.85</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6682.36</v>
+        <v>6469.28</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>14478.45</v>
+        <v>14016.78</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2784.32</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2784.32</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6682.36</v>
+        <v>6469.28</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>29792.19</v>
+        <v>28842.21</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2338.83</v>
+        <v>2264.25</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6682.36</v>
+        <v>6469.28</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11137.27</v>
+        <v>10782.14</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7796.09</v>
+        <v>7547.5</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2886.78</v>
+        <v>2794.73</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>32743.57</v>
+        <v>31699.48</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22274.54</v>
+        <v>21564.27</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4274.58</v>
+        <v>4190.28</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17151.39</v>
+        <v>16813.14</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13364.72</v>
+        <v>13101.15</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>25081.13</v>
+        <v>24586.49</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>12251</v>
+        <v>12009.39</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6682.36</v>
+        <v>6550.58</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7796.09</v>
+        <v>7642.34</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8909.82</v>
+        <v>8734.1</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3341.18</v>
+        <v>3275.29</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8909.82</v>
+        <v>8734.1</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8188.22</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>389804.41</v>
+        <v>382116.93</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4454.91</v>
+        <v>4367.05</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>22831.4</v>
+        <v>22381.13</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5011.77</v>
+        <v>4912.93</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2335.12</v>
+        <v>2289.07</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5568.63</v>
+        <v>5458.81</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8521.040000000001</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2339.94</v>
+        <v>2293.79</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>584335.37</v>
+        <v>572811.47</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2780.09</v>
+        <v>2725.26</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2762.14</v>
+        <v>2707.67</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6682.36</v>
+        <v>6550.58</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3452.55</v>
+        <v>3384.46</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4454.91</v>
+        <v>4367.05</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4454.91</v>
+        <v>4367.05</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9466.68</v>
+        <v>9279.98</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>16868.32</v>
+        <v>16535.65</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4205.14</v>
+        <v>4122.21</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2338.83</v>
+        <v>2292.7</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>10580.41</v>
+        <v>10371.75</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2585.81</v>
+        <v>2517.71</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3341.18</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3341.18</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3898.04</v>
+        <v>3795.4</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25764.02</v>
+        <v>25085.57</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2338.83</v>
+        <v>2277.24</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6682.36</v>
+        <v>6506.39</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10023.54</v>
+        <v>9759.59</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2338.83</v>
+        <v>2277.24</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3675.3</v>
+        <v>3578.52</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5939.74</v>
+        <v>5783.33</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>14478.45</v>
+        <v>14097.18</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8909.82</v>
+        <v>8675.190000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>50117.71</v>
+        <v>48797.94</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13364.72</v>
+        <v>13012.79</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2561.57</v>
+        <v>2494.12</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>37866.71</v>
+        <v>36869.56</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4454.91</v>
+        <v>4337.6</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>23945.13</v>
+        <v>23314.57</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>8909.82</v>
+        <v>8675.190000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5791.38</v>
+        <v>5638.87</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3341.18</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>10023.54</v>
+        <v>9759.59</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3341.18</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>8909.82</v>
+        <v>8675.190000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>13364.72</v>
+        <v>13012.79</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>44549.08</v>
+        <v>43375.95</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>14478.45</v>
+        <v>14097.18</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2784.32</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>6682.36</v>
+        <v>6506.39</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2895.69</v>
+        <v>2819.44</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>11137.27</v>
+        <v>10843.99</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2450.2</v>
+        <v>2385.68</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>55686.34</v>
+        <v>54219.94</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2338.83</v>
+        <v>2277.24</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4521.73</v>
+        <v>4402.66</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6682.36</v>
+        <v>6506.39</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2394.51</v>
+        <v>2331.46</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>13364.72</v>
+        <v>13122.36</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3898.04</v>
+        <v>3827.35</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>24195.72</v>
+        <v>23756.93</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9188.25</v>
+        <v>9021.620000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>15592.18</v>
+        <v>15309.41</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>12251</v>
+        <v>12028.83</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>21160.81</v>
+        <v>20777.06</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>11137.27</v>
+        <v>10935.3</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2338.83</v>
+        <v>2296.41</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>33133.37</v>
+        <v>32532.51</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2338.83</v>
+        <v>2296.41</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6682.36</v>
+        <v>6561.18</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6682.36</v>
+        <v>6561.18</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>7796.09</v>
+        <v>7654.71</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5474.19</v>
+        <v>5374.92</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4676.13</v>
+        <v>4591.33</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4454.91</v>
+        <v>4374.12</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>16705.9</v>
+        <v>16402.94</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>5568.63</v>
+        <v>5467.65</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>55686.34</v>
+        <v>54676.48</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>33411.81</v>
+        <v>32805.89</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>11137.27</v>
+        <v>10935.3</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>14478.45</v>
+        <v>14215.88</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>11137.27</v>
+        <v>10935.3</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3898.04</v>
+        <v>3827.35</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3118.44</v>
+        <v>3061.88</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>27843.17</v>
+        <v>27338.24</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2784.32</v>
+        <v>2733.82</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2784.32</v>
+        <v>2733.82</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>22274.54</v>
+        <v>21870.59</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3341.18</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2784.32</v>
+        <v>2733.82</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2450.2</v>
+        <v>2405.77</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>27843.17</v>
+        <v>27338.24</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6056.06</v>
+        <v>5946.24</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3898.04</v>
+        <v>3827.35</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2338.83</v>
+        <v>2296.41</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2539.3</v>
+        <v>2471.3</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2335.49</v>
+        <v>2272.95</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3341.18</v>
+        <v>3251.72</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>35082.4</v>
+        <v>34143.01</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>16705.9</v>
+        <v>16258.58</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8909.82</v>
+        <v>8671.24</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>44549.08</v>
+        <v>43356.2</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2784.32</v>
+        <v>2709.76</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>7796.09</v>
+        <v>7587.34</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>55686.34</v>
+        <v>54195.25</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>11137.27</v>
+        <v>10839.05</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8909.82</v>
+        <v>8671.24</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6682.36</v>
+        <v>6503.43</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>24056.5</v>
+        <v>23412.35</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>23388.26</v>
+        <v>22762.01</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2338.83</v>
+        <v>2276.2</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3341.18</v>
+        <v>3251.72</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>6236.87</v>
+        <v>6069.87</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3341.18</v>
+        <v>3251.72</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5568.63</v>
+        <v>5419.53</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2450.2</v>
+        <v>2384.59</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1503512.42</v>
+        <v>1463253.51</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>16705.9</v>
+        <v>16258.58</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>33411.81</v>
+        <v>32517.15</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>36752.99</v>
+        <v>35768.87</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2338.83</v>
+        <v>2276.2</v>
       </c>
     </row>
     <row r="182">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5568.63</v>
+        <v>5419.53</v>
       </c>
     </row>
     <row r="183">
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>22274.54</v>
+        <v>21678.1</v>
       </c>
     </row>
     <row r="184">
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5568.63</v>
+        <v>5419.53</v>
       </c>
     </row>
     <row r="185">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2561.57</v>
+        <v>2492.98</v>
       </c>
     </row>
     <row r="186">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2335.49</v>
+        <v>2272.95</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>10023.54</v>
+        <v>9755.15</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>11137.27</v>
+        <v>10839.05</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2672.94</v>
+        <v>2601.37</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6682.36</v>
+        <v>6503.43</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2338.83</v>
+        <v>2276.2</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2561.57</v>
+        <v>2492.98</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>11137.27</v>
+        <v>11169.69</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7796.09</v>
+        <v>7818.78</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3341.18</v>
+        <v>3350.91</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>10673.96</v>
+        <v>10705.03</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2494.75</v>
+        <v>2502.01</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3341.18</v>
+        <v>3350.91</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5433.87</v>
+        <v>5449.69</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>22274.54</v>
+        <v>22339.38</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>55686.34</v>
+        <v>55848.45</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>36752.99</v>
+        <v>36859.98</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6236.87</v>
+        <v>6255.03</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>33411.81</v>
+        <v>33509.07</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>7796.09</v>
+        <v>7818.78</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2338.83</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6129.14</v>
+        <v>6146.98</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2338.83</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="209">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>8909.82</v>
+        <v>8935.75</v>
       </c>
     </row>
     <row r="210">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8909.82</v>
+        <v>8935.75</v>
       </c>
     </row>
     <row r="211">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3341.18</v>
+        <v>3350.91</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>73505.97</v>
+        <v>73719.95</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>5568.63</v>
+        <v>5584.84</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4287.85</v>
+        <v>4300.33</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>17819.63</v>
+        <v>17871.5</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2335.12</v>
+        <v>2341.92</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>6548.71</v>
+        <v>6567.78</v>
       </c>
     </row>
     <row r="218">
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2335.12</v>
+        <v>2341.92</v>
       </c>
     </row>
     <row r="219">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>26729.45</v>
+        <v>26807.26</v>
       </c>
     </row>
     <row r="220">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>15592.18</v>
+        <v>15637.57</v>
       </c>
     </row>
     <row r="221">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>20938.07</v>
+        <v>20999.02</v>
       </c>
     </row>
     <row r="222">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2338.83</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="223">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3341.18</v>
+        <v>3350.91</v>
       </c>
     </row>
     <row r="224">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2338.83</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="225">
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2450.2</v>
+        <v>2457.33</v>
       </c>
     </row>
     <row r="226">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>34525.53</v>
+        <v>34626.04</v>
       </c>
     </row>
     <row r="227">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>33411.81</v>
+        <v>33509.07</v>
       </c>
     </row>
     <row r="228">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3898.04</v>
+        <v>3909.39</v>
       </c>
     </row>
     <row r="229">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>5414.12</v>
+        <v>5436.63</v>
       </c>
     </row>
     <row r="230">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2361.1</v>
+        <v>2370.91</v>
       </c>
     </row>
     <row r="231">
@@ -14550,7 +14550,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>37866.71</v>
+        <v>38024.09</v>
       </c>
     </row>
     <row r="232">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.49</v>
       </c>
     </row>
     <row r="233">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.49</v>
       </c>
     </row>
     <row r="234">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>11137.27</v>
+        <v>11183.56</v>
       </c>
     </row>
     <row r="235">
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="236">
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="237">
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>6302.83</v>
+        <v>6329.03</v>
       </c>
     </row>
     <row r="238">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>7848.43</v>
+        <v>7881.05</v>
       </c>
     </row>
     <row r="239">
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="240">
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>23388.26</v>
+        <v>23485.47</v>
       </c>
     </row>
     <row r="241">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12251</v>
+        <v>12301.91</v>
       </c>
     </row>
     <row r="242">
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>11137.27</v>
+        <v>11183.56</v>
       </c>
     </row>
     <row r="243">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>33411.81</v>
+        <v>33550.67</v>
       </c>
     </row>
     <row r="244">
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>36953.46</v>
+        <v>37107.04</v>
       </c>
     </row>
     <row r="245">
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="246">
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="247">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>13364.72</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="248">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="249">
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>35846.64</v>
+        <v>35995.62</v>
       </c>
     </row>
     <row r="250">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>13364.72</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="251">
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2338.83</v>
+        <v>2348.55</v>
       </c>
     </row>
     <row r="252">
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>8909.82</v>
+        <v>8946.84</v>
       </c>
     </row>
     <row r="253">
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>8909.82</v>
+        <v>8946.84</v>
       </c>
     </row>
     <row r="254">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7239.22</v>
+        <v>7269.31</v>
       </c>
     </row>
     <row r="255">
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>26172.58</v>
+        <v>26281.36</v>
       </c>
     </row>
     <row r="256">
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="257">
@@ -16136,7 +16136,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2450.2</v>
+        <v>2460.38</v>
       </c>
     </row>
     <row r="258">
@@ -16197,7 +16197,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="259">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="260">
@@ -16319,7 +16319,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>9133.08</v>
+        <v>9171.030000000001</v>
       </c>
     </row>
     <row r="261">
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="262">
@@ -16441,7 +16441,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>15592.18</v>
+        <v>15656.98</v>
       </c>
     </row>
     <row r="263">
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>15592.18</v>
+        <v>15656.98</v>
       </c>
     </row>
     <row r="264">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2784.32</v>
+        <v>2795.89</v>
       </c>
     </row>
     <row r="265">
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.49</v>
       </c>
     </row>
     <row r="266">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.24</v>
       </c>
     </row>
     <row r="267">
@@ -16746,7 +16746,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="268">
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>26506.7</v>
+        <v>26616.86</v>
       </c>
     </row>
     <row r="269">
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.78</v>
       </c>
     </row>
     <row r="270">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2450.2</v>
+        <v>2460.38</v>
       </c>
     </row>
     <row r="271">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2784.32</v>
+        <v>2795.89</v>
       </c>
     </row>
     <row r="272">
@@ -17051,7 +17051,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>27843.17</v>
+        <v>27958.89</v>
       </c>
     </row>
     <row r="273">
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>12528.31</v>
+        <v>12580.38</v>
       </c>
     </row>
     <row r="274">
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5401.58</v>
+        <v>5424.02</v>
       </c>
     </row>
     <row r="275">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2993.03</v>
+        <v>3018.43</v>
       </c>
     </row>
     <row r="276">
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3341.18</v>
+        <v>3369.54</v>
       </c>
     </row>
     <row r="277">
@@ -17356,7 +17356,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8575.700000000001</v>
+        <v>8648.48</v>
       </c>
     </row>
     <row r="278">
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2338.83</v>
+        <v>2358.68</v>
       </c>
     </row>
     <row r="279">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>6974.63</v>
+        <v>7033.82</v>
       </c>
     </row>
     <row r="280">
@@ -17539,7 +17539,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5568.63</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="281">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3091.71</v>
+        <v>3117.95</v>
       </c>
     </row>
     <row r="282">
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="283">
@@ -17722,7 +17722,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2338.83</v>
+        <v>2358.68</v>
       </c>
     </row>
     <row r="284">
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>8682.940000000001</v>
+        <v>8756.639999999999</v>
       </c>
     </row>
     <row r="285">
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>11137.27</v>
+        <v>11231.79</v>
       </c>
     </row>
     <row r="286">
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5305.79</v>
+        <v>5350.82</v>
       </c>
     </row>
     <row r="287">
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>53158.18</v>
+        <v>53609.34</v>
       </c>
     </row>
     <row r="288">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>27843.17</v>
+        <v>28079.48</v>
       </c>
     </row>
     <row r="289">
@@ -18088,7 +18088,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>37609.08</v>
+        <v>37928.26</v>
       </c>
     </row>
     <row r="290">
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>77837.25999999999</v>
+        <v>78497.86</v>
       </c>
     </row>
     <row r="291">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>16705.9</v>
+        <v>16847.69</v>
       </c>
     </row>
     <row r="292">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2895.69</v>
+        <v>2920.27</v>
       </c>
     </row>
     <row r="293">
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3341.18</v>
+        <v>3369.54</v>
       </c>
     </row>
     <row r="294">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>34525.53</v>
+        <v>34818.55</v>
       </c>
     </row>
     <row r="295">
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2335.49</v>
+        <v>2355.31</v>
       </c>
     </row>
     <row r="296">
@@ -18515,7 +18515,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="297">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>6682.36</v>
+        <v>6739.07</v>
       </c>
     </row>
     <row r="298">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>7783.73</v>
+        <v>7849.79</v>
       </c>
     </row>
     <row r="299">
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="300">
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>55686.34</v>
+        <v>56158.95</v>
       </c>
     </row>
     <row r="301">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2450.2</v>
+        <v>2470.99</v>
       </c>
     </row>
     <row r="302">
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3341.18</v>
+        <v>3369.54</v>
       </c>
     </row>
     <row r="303">
@@ -18942,7 +18942,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5568.63</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="304">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>5568.63</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="305">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>11137.27</v>
+        <v>11231.79</v>
       </c>
     </row>
     <row r="306">
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3390.66</v>
+        <v>3419.43</v>
       </c>
     </row>
     <row r="307">
@@ -19186,7 +19186,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2338.83</v>
+        <v>2358.68</v>
       </c>
     </row>
     <row r="308">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="309">
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2338.83</v>
+        <v>2358.68</v>
       </c>
     </row>
     <row r="310">
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>26998.97</v>
+        <v>27228.11</v>
       </c>
     </row>
     <row r="311">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>4566.28</v>
+        <v>4605.03</v>
       </c>
     </row>
     <row r="312">
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>33411.81</v>
+        <v>33355.94</v>
       </c>
     </row>
     <row r="313">
@@ -19552,7 +19552,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>7461.97</v>
+        <v>7449.49</v>
       </c>
     </row>
     <row r="314">
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3842.36</v>
+        <v>3835.93</v>
       </c>
     </row>
     <row r="315">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>4402.51</v>
+        <v>4395.15</v>
       </c>
     </row>
     <row r="316">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>16705.9</v>
+        <v>16677.97</v>
       </c>
     </row>
     <row r="317">
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3118.44</v>
+        <v>3113.22</v>
       </c>
     </row>
     <row r="318">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2784.32</v>
+        <v>2779.66</v>
       </c>
     </row>
     <row r="319">
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>11137.27</v>
+        <v>11118.65</v>
       </c>
     </row>
     <row r="320">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="321">
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>46776.53</v>
+        <v>46698.32</v>
       </c>
     </row>
     <row r="322">
@@ -20101,7 +20101,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="323">
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>6682.36</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="324">
@@ -20223,7 +20223,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>37866.71</v>
+        <v>37803.4</v>
       </c>
     </row>
     <row r="325">
@@ -20284,7 +20284,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>22274.54</v>
+        <v>22237.29</v>
       </c>
     </row>
     <row r="326">
@@ -20345,7 +20345,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>22274.54</v>
+        <v>22237.29</v>
       </c>
     </row>
     <row r="327">
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>20047.08</v>
+        <v>20013.56</v>
       </c>
     </row>
     <row r="328">
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5011.77</v>
+        <v>5003.39</v>
       </c>
     </row>
     <row r="329">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5011.77</v>
+        <v>5003.39</v>
       </c>
     </row>
     <row r="330">
@@ -20589,7 +20589,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="331">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="332">
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>27843.17</v>
+        <v>27796.62</v>
       </c>
     </row>
     <row r="333">
@@ -20772,7 +20772,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>11137.27</v>
+        <v>11118.65</v>
       </c>
     </row>
     <row r="334">
@@ -20833,7 +20833,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>7239.22</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="335">
@@ -20894,7 +20894,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2338.83</v>
+        <v>2334.92</v>
       </c>
     </row>
     <row r="336">
@@ -20955,7 +20955,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>11137.27</v>
+        <v>11118.65</v>
       </c>
     </row>
     <row r="337">
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>5568.63</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="338">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="339">
@@ -21138,7 +21138,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>11137.27</v>
+        <v>11118.65</v>
       </c>
     </row>
     <row r="340">
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="341">
@@ -21260,7 +21260,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>26729.45</v>
+        <v>26684.75</v>
       </c>
     </row>
     <row r="342">
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>133647.23</v>
+        <v>133423.76</v>
       </c>
     </row>
     <row r="343">
@@ -21382,7 +21382,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3620.79</v>
+        <v>3614.74</v>
       </c>
     </row>
     <row r="344">
@@ -21443,7 +21443,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>6014.13</v>
+        <v>6004.07</v>
       </c>
     </row>
     <row r="345">
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>7239.22</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="346">
@@ -21565,7 +21565,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>22274.54</v>
+        <v>22237.29</v>
       </c>
     </row>
     <row r="347">
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>7096.53</v>
+        <v>7084.66</v>
       </c>
     </row>
     <row r="348">
@@ -21687,7 +21687,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>5568.63</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="349">
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6905.11</v>
+        <v>6893.56</v>
       </c>
     </row>
     <row r="350">
@@ -21809,7 +21809,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2338.83</v>
+        <v>2334.92</v>
       </c>
     </row>
     <row r="351">
@@ -21870,7 +21870,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>24501.99</v>
+        <v>24461.02</v>
       </c>
     </row>
     <row r="352">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>7796.09</v>
+        <v>7783.05</v>
       </c>
     </row>
     <row r="353">
@@ -21992,7 +21992,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="354">
@@ -22053,7 +22053,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>37866.71</v>
+        <v>37803.4</v>
       </c>
     </row>
     <row r="355">
@@ -22114,7 +22114,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>15146.69</v>
+        <v>15121.36</v>
       </c>
     </row>
     <row r="356">
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>5463.22</v>
+        <v>5454.09</v>
       </c>
     </row>
     <row r="357">
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>27843.17</v>
+        <v>27796.62</v>
       </c>
     </row>
     <row r="358">
@@ -22301,7 +22301,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>333004.34</v>
+        <v>332447.55</v>
       </c>
     </row>
     <row r="359">
@@ -22362,7 +22362,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="360">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>16705.9</v>
+        <v>16677.97</v>
       </c>
     </row>
     <row r="361">
@@ -22484,7 +22484,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>22274.54</v>
+        <v>22237.29</v>
       </c>
     </row>
     <row r="362">
@@ -22545,7 +22545,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>6682.36</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="363">
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>3007.06</v>
+        <v>3002.03</v>
       </c>
     </row>
     <row r="364">
@@ -22667,7 +22667,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="365">
@@ -22728,7 +22728,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>6682.36</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="366">
@@ -22789,7 +22789,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2784.32</v>
+        <v>2779.66</v>
       </c>
     </row>
     <row r="367">
@@ -22850,7 +22850,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>17697.12</v>
+        <v>17667.53</v>
       </c>
     </row>
     <row r="368">
@@ -22911,7 +22911,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>14546.72</v>
+        <v>14522.4</v>
       </c>
     </row>
     <row r="369">
@@ -22972,7 +22972,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>5568.63</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="370">
@@ -23033,7 +23033,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="371">
@@ -23094,7 +23094,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>27843.17</v>
+        <v>28185.85</v>
       </c>
     </row>
     <row r="372">
@@ -23155,7 +23155,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2338.83</v>
+        <v>2367.61</v>
       </c>
     </row>
     <row r="373">
@@ -23216,7 +23216,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2872.25</v>
+        <v>2907.6</v>
       </c>
     </row>
     <row r="374">
@@ -23277,7 +23277,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>13364.72</v>
+        <v>13529.21</v>
       </c>
     </row>
     <row r="375">
@@ -23338,7 +23338,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>54238.5</v>
+        <v>54906.03</v>
       </c>
     </row>
     <row r="376">
@@ -23399,7 +23399,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="377">
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>4454.91</v>
+        <v>4509.74</v>
       </c>
     </row>
     <row r="378">
@@ -23521,7 +23521,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>7796.09</v>
+        <v>7892.04</v>
       </c>
     </row>
     <row r="379">
@@ -23582,7 +23582,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="380">
@@ -23643,7 +23643,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>16705.9</v>
+        <v>16911.51</v>
       </c>
     </row>
     <row r="381">
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="382">
@@ -23765,7 +23765,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3007.06</v>
+        <v>3044.07</v>
       </c>
     </row>
     <row r="383">
@@ -23826,7 +23826,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4948.29</v>
+        <v>5009.19</v>
       </c>
     </row>
     <row r="384">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>26729.45</v>
+        <v>27058.41</v>
       </c>
     </row>
     <row r="385">
@@ -23948,7 +23948,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>12419.68</v>
+        <v>12572.53</v>
       </c>
     </row>
     <row r="386">
@@ -24009,7 +24009,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2338.83</v>
+        <v>2367.61</v>
       </c>
     </row>
     <row r="387">
@@ -24070,7 +24070,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3007.06</v>
+        <v>3044.07</v>
       </c>
     </row>
     <row r="388">
@@ -24131,7 +24131,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>11862.26</v>
+        <v>12008.26</v>
       </c>
     </row>
     <row r="389">
@@ -24192,7 +24192,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>22274.54</v>
+        <v>22548.68</v>
       </c>
     </row>
     <row r="390">
@@ -24253,7 +24253,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>16705.9</v>
+        <v>16911.51</v>
       </c>
     </row>
     <row r="391">
@@ -24314,7 +24314,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>33411.81</v>
+        <v>33823.02</v>
       </c>
     </row>
     <row r="392">
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="393">
@@ -24436,7 +24436,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>16705.9</v>
+        <v>16911.51</v>
       </c>
     </row>
     <row r="394">
@@ -24497,7 +24497,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4399.22</v>
+        <v>4453.36</v>
       </c>
     </row>
     <row r="395">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2338.83</v>
+        <v>2367.61</v>
       </c>
     </row>
     <row r="396">
@@ -24619,7 +24619,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>10023.54</v>
+        <v>10146.9</v>
       </c>
     </row>
     <row r="397">
@@ -24680,7 +24680,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="398">
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>3786.67</v>
+        <v>3833.28</v>
       </c>
     </row>
     <row r="399">
@@ -24802,7 +24802,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>4844.71</v>
+        <v>4904.34</v>
       </c>
     </row>
     <row r="400">
@@ -24863,7 +24863,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>10023.54</v>
+        <v>10146.9</v>
       </c>
     </row>
     <row r="401">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="402">
@@ -24985,7 +24985,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="403">
@@ -25046,7 +25046,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2338.83</v>
+        <v>2367.61</v>
       </c>
     </row>
     <row r="404">
@@ -25107,7 +25107,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3898.04</v>
+        <v>3946.02</v>
       </c>
     </row>
     <row r="405">
@@ -25168,7 +25168,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>36752.99</v>
+        <v>37205.32</v>
       </c>
     </row>
     <row r="406">
@@ -25229,7 +25229,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="407">
@@ -25290,7 +25290,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>4350.76</v>
+        <v>4404.3</v>
       </c>
     </row>
     <row r="408">
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>6682.36</v>
+        <v>6764.6</v>
       </c>
     </row>
     <row r="409">
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="410">
@@ -25473,7 +25473,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>4454.91</v>
+        <v>4509.74</v>
       </c>
     </row>
     <row r="411">
@@ -25534,7 +25534,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="412">
@@ -25595,7 +25595,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>5054.75</v>
+        <v>5116.96</v>
       </c>
     </row>
     <row r="413">
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2335.12</v>
+        <v>2363.86</v>
       </c>
     </row>
     <row r="414">
@@ -25717,7 +25717,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>11249.36</v>
+        <v>11387.81</v>
       </c>
     </row>
     <row r="415">
@@ -25778,7 +25778,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="416">
@@ -25839,7 +25839,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="417">
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="418">
@@ -25961,7 +25961,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>4454.91</v>
+        <v>4509.74</v>
       </c>
     </row>
     <row r="419">
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4454.91</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="420">
@@ -26083,7 +26083,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2450.2</v>
+        <v>2482.82</v>
       </c>
     </row>
     <row r="421">
@@ -26144,7 +26144,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>4454.91</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="422">
@@ -26205,7 +26205,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="423">
@@ -26266,7 +26266,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="424">
@@ -26327,7 +26327,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>7872.74</v>
+        <v>7977.55</v>
       </c>
     </row>
     <row r="425">
@@ -26388,7 +26388,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>15592.18</v>
+        <v>15799.75</v>
       </c>
     </row>
     <row r="426">
@@ -26449,7 +26449,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>7684.72</v>
+        <v>7787.02</v>
       </c>
     </row>
     <row r="427">
@@ -26510,7 +26510,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>7796.09</v>
+        <v>7899.87</v>
       </c>
     </row>
     <row r="428">
@@ -26571,7 +26571,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>8464.32</v>
+        <v>8577.01</v>
       </c>
     </row>
     <row r="429">
@@ -26632,7 +26632,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="430">
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="431">
@@ -26754,7 +26754,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="432">
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>7796.09</v>
+        <v>7899.87</v>
       </c>
     </row>
     <row r="433">
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>4508.9</v>
+        <v>4568.92</v>
       </c>
     </row>
     <row r="434">
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>7836.18</v>
+        <v>7940.5</v>
       </c>
     </row>
     <row r="435">
@@ -26998,7 +26998,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.96</v>
       </c>
     </row>
     <row r="436">
@@ -27059,7 +27059,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="437">
@@ -27120,7 +27120,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>9026.76</v>
+        <v>9146.93</v>
       </c>
     </row>
     <row r="438">
@@ -27181,7 +27181,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3341.18</v>
+        <v>3385.66</v>
       </c>
     </row>
     <row r="439">
@@ -27242,7 +27242,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.96</v>
       </c>
     </row>
     <row r="440">
@@ -27303,7 +27303,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>6125.5</v>
+        <v>6207.04</v>
       </c>
     </row>
     <row r="441">
@@ -27364,7 +27364,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>10023.54</v>
+        <v>10156.98</v>
       </c>
     </row>
     <row r="442">
@@ -27425,7 +27425,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>38980.44</v>
+        <v>39499.37</v>
       </c>
     </row>
     <row r="443">
@@ -27486,7 +27486,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>16705.9</v>
+        <v>16928.3</v>
       </c>
     </row>
     <row r="444">
@@ -27547,7 +27547,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>14798.86</v>
+        <v>14995.87</v>
       </c>
     </row>
     <row r="445">
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2335.12</v>
+        <v>2366.2</v>
       </c>
     </row>
     <row r="446">
@@ -27669,7 +27669,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>29433.13</v>
+        <v>29824.97</v>
       </c>
     </row>
     <row r="447">
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>12707.62</v>
+        <v>12876.8</v>
       </c>
     </row>
     <row r="448">
@@ -27791,7 +27791,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="449">
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>4454.91</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="450">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.96</v>
       </c>
     </row>
     <row r="451">
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>3898.04</v>
+        <v>3949.94</v>
       </c>
     </row>
     <row r="452">
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="453">
@@ -28096,7 +28096,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>38002.77</v>
+        <v>38508.69</v>
       </c>
     </row>
     <row r="454">
@@ -28157,7 +28157,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>6682.36</v>
+        <v>6771.32</v>
       </c>
     </row>
     <row r="455">
@@ -28218,7 +28218,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2784.32</v>
+        <v>2821.38</v>
       </c>
     </row>
     <row r="456">
@@ -28279,7 +28279,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>28400.04</v>
+        <v>28778.12</v>
       </c>
     </row>
     <row r="457">
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>13271.5</v>
+        <v>13448.18</v>
       </c>
     </row>
     <row r="458">
@@ -28401,7 +28401,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>12528.31</v>
+        <v>12695.1</v>
       </c>
     </row>
     <row r="459">
@@ -28462,7 +28462,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>6682.36</v>
+        <v>6771.32</v>
       </c>
     </row>
     <row r="460">
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.96</v>
       </c>
     </row>
     <row r="461">
@@ -28584,7 +28584,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>11137.27</v>
+        <v>11285.54</v>
       </c>
     </row>
     <row r="462">
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2335.12</v>
+        <v>2366.2</v>
       </c>
     </row>
     <row r="463">
@@ -28706,7 +28706,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>2335.12</v>
+        <v>2366.2</v>
       </c>
     </row>
     <row r="464">
@@ -28767,7 +28767,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>34547.81</v>
+        <v>35007.73</v>
       </c>
     </row>
     <row r="465">
@@ -28828,7 +28828,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>8909.82</v>
+        <v>9028.43</v>
       </c>
     </row>
     <row r="466">
@@ -28889,7 +28889,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>14478.45</v>
+        <v>14671.2</v>
       </c>
     </row>
     <row r="467">
@@ -28950,7 +28950,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>17536.47</v>
+        <v>17769.92</v>
       </c>
     </row>
     <row r="468">
@@ -29011,7 +29011,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>7796.09</v>
+        <v>7899.87</v>
       </c>
     </row>
     <row r="469">
@@ -29072,7 +29072,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>6463.63</v>
+        <v>6549.67</v>
       </c>
     </row>
     <row r="470">
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.96</v>
       </c>
     </row>
     <row r="471">
@@ -29198,7 +29198,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>155921.76</v>
+        <v>157997.49</v>
       </c>
     </row>
     <row r="472">
@@ -29259,7 +29259,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>6682.36</v>
+        <v>6771.32</v>
       </c>
     </row>
     <row r="473">
@@ -29320,7 +29320,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3341.18</v>
+        <v>3385.66</v>
       </c>
     </row>
     <row r="474">
@@ -29381,7 +29381,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2335.49</v>
+        <v>2366.58</v>
       </c>
     </row>
     <row r="475">
@@ -29442,7 +29442,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="476">
@@ -29503,7 +29503,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>11137.27</v>
+        <v>11282.61</v>
       </c>
     </row>
     <row r="477">
@@ -29564,7 +29564,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>18098.06</v>
+        <v>18334.24</v>
       </c>
     </row>
     <row r="478">
@@ -29625,7 +29625,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>8909.82</v>
+        <v>9026.09</v>
       </c>
     </row>
     <row r="479">
@@ -29686,7 +29686,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4454.91</v>
+        <v>4513.04</v>
       </c>
     </row>
     <row r="480">
@@ -29747,7 +29747,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2450.2</v>
+        <v>2482.17</v>
       </c>
     </row>
     <row r="481">
@@ -29808,7 +29808,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>12251</v>
+        <v>12410.87</v>
       </c>
     </row>
     <row r="482">
@@ -29869,7 +29869,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.35</v>
       </c>
     </row>
     <row r="483">
@@ -29934,7 +29934,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>112300.79</v>
+        <v>113766.28</v>
       </c>
     </row>
     <row r="484">
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4654.71</v>
+        <v>4715.45</v>
       </c>
     </row>
     <row r="485">
@@ -30056,7 +30056,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>3341.18</v>
+        <v>3384.78</v>
       </c>
     </row>
     <row r="486">
@@ -30117,7 +30117,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="487">
@@ -30178,7 +30178,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="488">
@@ -30239,7 +30239,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>7796.09</v>
+        <v>7897.82</v>
       </c>
     </row>
     <row r="489">
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>72392.25</v>
+        <v>73336.94</v>
       </c>
     </row>
     <row r="490">
@@ -30361,7 +30361,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>33411.81</v>
+        <v>33847.82</v>
       </c>
     </row>
     <row r="491">
@@ -30422,7 +30422,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="492">
@@ -30483,7 +30483,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="493">
@@ -30544,7 +30544,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>36752.99</v>
+        <v>37232.6</v>
       </c>
     </row>
     <row r="494">
@@ -30605,7 +30605,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>33411.81</v>
+        <v>33847.82</v>
       </c>
     </row>
     <row r="495">
@@ -30666,7 +30666,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>9281.059999999999</v>
+        <v>9402.17</v>
       </c>
     </row>
     <row r="496">
@@ -30727,7 +30727,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8461.959999999999</v>
       </c>
     </row>
     <row r="497">
@@ -30788,7 +30788,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>6465.78</v>
+        <v>6550.16</v>
       </c>
     </row>
     <row r="498">
@@ -30849,7 +30849,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>27843.17</v>
+        <v>28206.52</v>
       </c>
     </row>
     <row r="499">
@@ -30910,7 +30910,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2338.83</v>
+        <v>2369.35</v>
       </c>
     </row>
     <row r="500">
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>7350.6</v>
+        <v>7446.52</v>
       </c>
     </row>
     <row r="501">
@@ -31032,7 +31032,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>26729.45</v>
+        <v>27078.26</v>
       </c>
     </row>
     <row r="502">
@@ -31093,7 +31093,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>7796.09</v>
+        <v>7897.82</v>
       </c>
     </row>
     <row r="503">
@@ -31154,7 +31154,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2335.12</v>
+        <v>2365.59</v>
       </c>
     </row>
     <row r="504">
@@ -31215,7 +31215,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>6069.81</v>
+        <v>6149.02</v>
       </c>
     </row>
     <row r="505">
@@ -31276,7 +31276,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2728.63</v>
+        <v>2764.24</v>
       </c>
     </row>
     <row r="506">
@@ -31337,7 +31337,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>22274.54</v>
+        <v>22565.21</v>
       </c>
     </row>
     <row r="507">
@@ -31398,7 +31398,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2784.32</v>
+        <v>2820.65</v>
       </c>
     </row>
     <row r="508">
@@ -31459,7 +31459,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>10023.54</v>
+        <v>10154.35</v>
       </c>
     </row>
     <row r="509">
@@ -31520,7 +31520,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>11137.27</v>
+        <v>11282.61</v>
       </c>
     </row>
     <row r="510">
@@ -31581,7 +31581,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2335.12</v>
+        <v>2365.59</v>
       </c>
     </row>
     <row r="511">
@@ -31642,7 +31642,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>6228.95</v>
+        <v>6382.25</v>
       </c>
     </row>
     <row r="512">
@@ -31703,7 +31703,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>12251</v>
+        <v>12552.49</v>
       </c>
     </row>
     <row r="513">
@@ -31764,7 +31764,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>37866.71</v>
+        <v>38798.61</v>
       </c>
     </row>
     <row r="514">
@@ -31825,7 +31825,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2895.69</v>
+        <v>2966.95</v>
       </c>
     </row>
     <row r="515">
@@ -31886,7 +31886,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>5568.63</v>
+        <v>5705.68</v>
       </c>
     </row>
     <row r="516">
@@ -31947,7 +31947,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3898.04</v>
+        <v>3993.97</v>
       </c>
     </row>
     <row r="517">
@@ -32008,7 +32008,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>22274.54</v>
+        <v>22822.71</v>
       </c>
     </row>
     <row r="518">
@@ -32069,7 +32069,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>16705.9</v>
+        <v>17117.03</v>
       </c>
     </row>
     <row r="519">
@@ -32130,7 +32130,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2450.2</v>
+        <v>2510.5</v>
       </c>
     </row>
     <row r="520">
@@ -32191,7 +32191,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>2561.57</v>
+        <v>2624.61</v>
       </c>
     </row>
     <row r="521">
@@ -32252,7 +32252,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>33411.81</v>
+        <v>34234.07</v>
       </c>
     </row>
     <row r="522">
@@ -32313,7 +32313,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>4714.48</v>
+        <v>4830.51</v>
       </c>
     </row>
     <row r="523">
@@ -32374,7 +32374,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>4454.91</v>
+        <v>4564.54</v>
       </c>
     </row>
     <row r="524">
@@ -32435,7 +32435,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>11137.27</v>
+        <v>11411.36</v>
       </c>
     </row>
     <row r="525">
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="526">
@@ -32557,7 +32557,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>4309.3</v>
+        <v>4415.35</v>
       </c>
     </row>
     <row r="527">
@@ -32618,7 +32618,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>11137.27</v>
+        <v>11411.36</v>
       </c>
     </row>
     <row r="528">
@@ -32679,7 +32679,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>11137.27</v>
+        <v>11411.36</v>
       </c>
     </row>
     <row r="529">
@@ -32740,7 +32740,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="530">
@@ -32801,7 +32801,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>8820.719999999999</v>
+        <v>9037.790000000001</v>
       </c>
     </row>
     <row r="531">
@@ -32862,7 +32862,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="532">
@@ -32923,7 +32923,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2338.83</v>
+        <v>2396.38</v>
       </c>
     </row>
     <row r="533">
@@ -32984,7 +32984,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="534">
@@ -33045,7 +33045,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2450.2</v>
+        <v>2510.5</v>
       </c>
     </row>
     <row r="535">
@@ -33106,7 +33106,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>31778.95</v>
+        <v>32561.02</v>
       </c>
     </row>
     <row r="536">
@@ -33167,7 +33167,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="537">
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>31614.25</v>
+        <v>32392.28</v>
       </c>
     </row>
     <row r="538">
@@ -33289,7 +33289,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2450.2</v>
+        <v>2510.5</v>
       </c>
     </row>
     <row r="539">
@@ -33350,7 +33350,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2784.32</v>
+        <v>2836.98</v>
       </c>
     </row>
     <row r="540">
@@ -33411,7 +33411,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>10605</v>
+        <v>10805.57</v>
       </c>
     </row>
     <row r="541">
@@ -33472,7 +33472,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>27843.17</v>
+        <v>28369.76</v>
       </c>
     </row>
     <row r="542">
@@ -33533,7 +33533,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>4454.91</v>
+        <v>4539.16</v>
       </c>
     </row>
     <row r="543">
@@ -33594,7 +33594,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>22274.54</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="544">
@@ -33655,7 +33655,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>3341.18</v>
+        <v>3404.37</v>
       </c>
     </row>
     <row r="545">
@@ -33716,7 +33716,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>4454.91</v>
+        <v>4539.16</v>
       </c>
     </row>
     <row r="546">
@@ -33777,7 +33777,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>11137.27</v>
+        <v>11347.9</v>
       </c>
     </row>
     <row r="547">
@@ -33838,7 +33838,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>10023.54</v>
+        <v>10213.11</v>
       </c>
     </row>
     <row r="548">
@@ -33899,7 +33899,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>9837.549999999999</v>
+        <v>10023.6</v>
       </c>
     </row>
     <row r="549">
@@ -33960,7 +33960,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>2335.12</v>
+        <v>2379.28</v>
       </c>
     </row>
     <row r="550">
@@ -34021,7 +34021,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>3341.18</v>
+        <v>3404.37</v>
       </c>
     </row>
     <row r="551">
@@ -34082,7 +34082,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>16705.9</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="552">
@@ -34143,7 +34143,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2784.32</v>
+        <v>2836.98</v>
       </c>
     </row>
     <row r="553">
@@ -34204,7 +34204,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>36752.99</v>
+        <v>37448.08</v>
       </c>
     </row>
     <row r="554">
@@ -34265,7 +34265,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>6682.36</v>
+        <v>6808.74</v>
       </c>
     </row>
     <row r="555">
@@ -34326,7 +34326,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>6014.13</v>
+        <v>6127.87</v>
       </c>
     </row>
     <row r="556">
@@ -34387,7 +34387,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>6682.36</v>
+        <v>6808.74</v>
       </c>
     </row>
     <row r="557">
@@ -34448,7 +34448,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2338.83</v>
+        <v>2383.06</v>
       </c>
     </row>
     <row r="558">
@@ -34509,7 +34509,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>5244.7</v>
+        <v>5343.9</v>
       </c>
     </row>
     <row r="559">
@@ -34570,7 +34570,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2338.83</v>
+        <v>2383.06</v>
       </c>
     </row>
     <row r="560">
@@ -34631,7 +34631,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2450.2</v>
+        <v>2496.54</v>
       </c>
     </row>
     <row r="561">
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>5568.63</v>
+        <v>5673.95</v>
       </c>
     </row>
     <row r="562">
@@ -34753,7 +34753,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>5568.63</v>
+        <v>5673.95</v>
       </c>
     </row>
     <row r="563">
@@ -34814,7 +34814,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4176.48</v>
+        <v>4255.46</v>
       </c>
     </row>
     <row r="564">
@@ -34875,7 +34875,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>25615.72</v>
+        <v>26100.18</v>
       </c>
     </row>
     <row r="565">
@@ -34936,7 +34936,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>3898.04</v>
+        <v>3971.77</v>
       </c>
     </row>
     <row r="566">
@@ -34997,7 +34997,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>8909.82</v>
+        <v>9078.32</v>
       </c>
     </row>
     <row r="567">
@@ -35058,7 +35058,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>22274.54</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="568">
@@ -35119,7 +35119,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>22274.54</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="569">
@@ -35180,7 +35180,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>9142.870000000001</v>
+        <v>9315.790000000001</v>
       </c>
     </row>
     <row r="570">
@@ -35241,7 +35241,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8510.93</v>
       </c>
     </row>
     <row r="571">
@@ -35302,7 +35302,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>16705.9</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="572">
@@ -35363,7 +35363,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>26813.36</v>
+        <v>27320.47</v>
       </c>
     </row>
     <row r="573">
@@ -35424,7 +35424,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>2711.65</v>
+        <v>2762.93</v>
       </c>
     </row>
     <row r="574">
@@ -35485,7 +35485,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>3341.18</v>
+        <v>3404.37</v>
       </c>
     </row>
     <row r="575">
@@ -35546,7 +35546,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>5011.77</v>
+        <v>5106.56</v>
       </c>
     </row>
     <row r="576">
@@ -35607,7 +35607,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>13364.72</v>
+        <v>13617.48</v>
       </c>
     </row>
     <row r="577">
@@ -35733,7 +35733,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>44549.08</v>
+        <v>45055.7</v>
       </c>
     </row>
     <row r="579">
@@ -35794,7 +35794,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>2450.2</v>
+        <v>2478.06</v>
       </c>
     </row>
     <row r="580">
@@ -35855,7 +35855,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2338.83</v>
+        <v>2365.42</v>
       </c>
     </row>
     <row r="581">
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>46776.53</v>
+        <v>47308.49</v>
       </c>
     </row>
     <row r="582">
@@ -35977,7 +35977,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>8909.82</v>
+        <v>9011.139999999999</v>
       </c>
     </row>
     <row r="583">
@@ -36038,7 +36038,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>17819.63</v>
+        <v>18022.28</v>
       </c>
     </row>
     <row r="584">
@@ -36103,7 +36103,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>334118.07</v>
+        <v>337917.75</v>
       </c>
     </row>
     <row r="585">
@@ -36164,7 +36164,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="586">
@@ -36225,7 +36225,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>17180.92</v>
+        <v>17376.31</v>
       </c>
     </row>
     <row r="587">
@@ -36286,7 +36286,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2338.83</v>
+        <v>2365.42</v>
       </c>
     </row>
     <row r="588">
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2784.32</v>
+        <v>2815.98</v>
       </c>
     </row>
     <row r="589">
@@ -36408,7 +36408,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5568.63</v>
+        <v>5631.96</v>
       </c>
     </row>
     <row r="590">
@@ -36469,7 +36469,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2338.83</v>
+        <v>2365.42</v>
       </c>
     </row>
     <row r="591">
@@ -36530,7 +36530,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>7796.09</v>
+        <v>7884.75</v>
       </c>
     </row>
     <row r="592">
@@ -36591,7 +36591,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>3118.44</v>
+        <v>3153.9</v>
       </c>
     </row>
     <row r="593">
@@ -36652,7 +36652,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>16705.9</v>
+        <v>16895.89</v>
       </c>
     </row>
     <row r="594">
@@ -36713,7 +36713,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>22274.54</v>
+        <v>22527.85</v>
       </c>
     </row>
     <row r="595">
@@ -36774,7 +36774,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>6682.36</v>
+        <v>6758.36</v>
       </c>
     </row>
     <row r="596">
@@ -36835,7 +36835,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8447.940000000001</v>
       </c>
     </row>
     <row r="597">
@@ -36896,7 +36896,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>18376.49</v>
+        <v>18585.48</v>
       </c>
     </row>
     <row r="598">
@@ -36957,7 +36957,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="599">
@@ -37018,7 +37018,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>5785.81</v>
+        <v>5851.61</v>
       </c>
     </row>
     <row r="600">
@@ -37079,7 +37079,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="601">
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3341.18</v>
+        <v>3379.18</v>
       </c>
     </row>
     <row r="602">
@@ -37201,7 +37201,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="603">
@@ -37262,7 +37262,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>7796.09</v>
+        <v>7884.75</v>
       </c>
     </row>
     <row r="604">
@@ -37323,7 +37323,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2806.47</v>
+        <v>2838.39</v>
       </c>
     </row>
     <row r="605">
@@ -37384,7 +37384,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="606">
@@ -37445,7 +37445,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>5011.77</v>
+        <v>5068.77</v>
       </c>
     </row>
     <row r="607">
@@ -37506,7 +37506,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>8909.82</v>
+        <v>9011.139999999999</v>
       </c>
     </row>
     <row r="608">
@@ -37567,7 +37567,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="609">
@@ -37628,7 +37628,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="610">
@@ -37689,7 +37689,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>5568.63</v>
+        <v>5631.96</v>
       </c>
     </row>
     <row r="611">
@@ -37750,7 +37750,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>17819.63</v>
+        <v>17980.15</v>
       </c>
     </row>
     <row r="612">
@@ -37811,7 +37811,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>22274.54</v>
+        <v>22475.19</v>
       </c>
     </row>
     <row r="613">
@@ -37872,7 +37872,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>8909.82</v>
+        <v>8990.08</v>
       </c>
     </row>
     <row r="614">
@@ -37933,7 +37933,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3675.3</v>
+        <v>3708.41</v>
       </c>
     </row>
     <row r="615">
@@ -37994,7 +37994,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="616">
@@ -38055,7 +38055,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>27843.17</v>
+        <v>28093.99</v>
       </c>
     </row>
     <row r="617">
@@ -38116,7 +38116,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>34748.28</v>
+        <v>35061.3</v>
       </c>
     </row>
     <row r="618">
@@ -38177,7 +38177,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>2450.2</v>
+        <v>2472.27</v>
       </c>
     </row>
     <row r="619">
@@ -38238,7 +38238,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>22274.54</v>
+        <v>22475.19</v>
       </c>
     </row>
     <row r="620">
@@ -38299,7 +38299,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>7796.09</v>
+        <v>7866.32</v>
       </c>
     </row>
     <row r="621">
@@ -38360,7 +38360,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>2784.32</v>
+        <v>2809.4</v>
       </c>
     </row>
     <row r="622">
@@ -38421,7 +38421,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>11137.27</v>
+        <v>11237.6</v>
       </c>
     </row>
     <row r="623">
@@ -38482,7 +38482,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>3844.73</v>
+        <v>3879.36</v>
       </c>
     </row>
     <row r="624">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>3341.18</v>
+        <v>3371.28</v>
       </c>
     </row>
     <row r="625">
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="626">
@@ -38665,7 +38665,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>4454.91</v>
+        <v>4495.04</v>
       </c>
     </row>
     <row r="627">
@@ -38726,7 +38726,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>6682.36</v>
+        <v>6742.56</v>
       </c>
     </row>
     <row r="628">
@@ -38787,7 +38787,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>8909.82</v>
+        <v>8990.08</v>
       </c>
     </row>
     <row r="629">
@@ -38848,7 +38848,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>3341.18</v>
+        <v>3371.28</v>
       </c>
     </row>
     <row r="630">
@@ -38909,7 +38909,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>3898.04</v>
+        <v>3933.16</v>
       </c>
     </row>
     <row r="631">
@@ -38970,7 +38970,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>3898.04</v>
+        <v>3933.16</v>
       </c>
     </row>
     <row r="632">
@@ -39031,7 +39031,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>5568.63</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="633">
@@ -39092,7 +39092,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>12793.38</v>
+        <v>12908.63</v>
       </c>
     </row>
     <row r="634">
@@ -39153,7 +39153,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="635">
@@ -39214,7 +39214,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>5011.77</v>
+        <v>5056.92</v>
       </c>
     </row>
     <row r="636">
@@ -39275,7 +39275,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2956.84</v>
+        <v>2983.47</v>
       </c>
     </row>
     <row r="637">
@@ -39336,7 +39336,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>16149.04</v>
+        <v>16294.51</v>
       </c>
     </row>
     <row r="638">
@@ -39397,7 +39397,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="639">
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>14300.25</v>
+        <v>14429.07</v>
       </c>
     </row>
     <row r="640">
@@ -39519,7 +39519,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2784.32</v>
+        <v>2809.4</v>
       </c>
     </row>
     <row r="641">
@@ -39580,7 +39580,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2358.87</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="642">
@@ -39641,7 +39641,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>91325.60000000001</v>
+        <v>92148.28999999999</v>
       </c>
     </row>
     <row r="643">
@@ -39702,7 +39702,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3898.04</v>
+        <v>3933.16</v>
       </c>
     </row>
     <row r="644">
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>37866.71</v>
+        <v>38207.83</v>
       </c>
     </row>
     <row r="645">
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>77058.89</v>
+        <v>77753.05</v>
       </c>
     </row>
     <row r="646">
@@ -39885,7 +39885,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>27843.17</v>
+        <v>28093.99</v>
       </c>
     </row>
     <row r="647">
@@ -39946,7 +39946,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>14330.1</v>
+        <v>14459.19</v>
       </c>
     </row>
     <row r="648">
@@ -40007,7 +40007,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>5568.63</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="649">
@@ -40068,7 +40068,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>8096.41</v>
+        <v>8169.35</v>
       </c>
     </row>
     <row r="650">
@@ -40129,7 +40129,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>5568.63</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="651">
@@ -40190,7 +40190,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>8864.6</v>
+        <v>8944.450000000001</v>
       </c>
     </row>
     <row r="652">
@@ -40251,7 +40251,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>11137.27</v>
+        <v>11237.6</v>
       </c>
     </row>
     <row r="653">
@@ -40312,7 +40312,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>13364.72</v>
+        <v>13485.12</v>
       </c>
     </row>
     <row r="654">
@@ -40373,7 +40373,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2895.69</v>
+        <v>2921.78</v>
       </c>
     </row>
     <row r="655">
@@ -40434,7 +40434,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>6682.36</v>
+        <v>6742.56</v>
       </c>
     </row>
     <row r="656">
@@ -40495,7 +40495,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="657">
@@ -40556,7 +40556,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>11137.27</v>
+        <v>11237.6</v>
       </c>
     </row>
     <row r="658">
@@ -40617,7 +40617,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>10023.54</v>
+        <v>10113.84</v>
       </c>
     </row>
     <row r="659">
@@ -40678,7 +40678,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>4454.91</v>
+        <v>4495.04</v>
       </c>
     </row>
     <row r="660">
@@ -40739,7 +40739,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>27910.22</v>
+        <v>28161.64</v>
       </c>
     </row>
     <row r="661">
@@ -40800,7 +40800,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>11404.56</v>
+        <v>11507.3</v>
       </c>
     </row>
     <row r="662">
@@ -40861,7 +40861,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>66823.61</v>
+        <v>67251</v>
       </c>
     </row>
     <row r="663">
@@ -40922,7 +40922,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="664">
@@ -40983,7 +40983,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>6002.99</v>
+        <v>6041.38</v>
       </c>
     </row>
     <row r="665">
@@ -41044,7 +41044,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>8909.82</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="666">
@@ -41105,7 +41105,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>6682.36</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="667">
@@ -41166,7 +41166,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>3341.18</v>
+        <v>3362.55</v>
       </c>
     </row>
     <row r="668">
@@ -41227,7 +41227,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>11137.27</v>
+        <v>11208.5</v>
       </c>
     </row>
     <row r="669">
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>13364.72</v>
+        <v>13450.2</v>
       </c>
     </row>
     <row r="670">
@@ -41349,7 +41349,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>7398</v>
+        <v>7445.32</v>
       </c>
     </row>
     <row r="671">
@@ -41410,7 +41410,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>6682.36</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="672">
@@ -41471,7 +41471,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>2338.83</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="673">
@@ -41532,7 +41532,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>6682.36</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="674">
@@ -41593,7 +41593,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>4454.91</v>
+        <v>4483.4</v>
       </c>
     </row>
     <row r="675">
@@ -41654,7 +41654,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>8909.82</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="676">
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>4454.91</v>
+        <v>4483.4</v>
       </c>
     </row>
     <row r="677">
@@ -41776,7 +41776,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>2338.83</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="678">
@@ -41837,7 +41837,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>7239.22</v>
+        <v>7285.53</v>
       </c>
     </row>
     <row r="679">
@@ -41898,7 +41898,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="680">
@@ -41959,7 +41959,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>7796.09</v>
+        <v>7845.95</v>
       </c>
     </row>
     <row r="681">
@@ -42020,7 +42020,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>9876.530000000001</v>
+        <v>9939.700000000001</v>
       </c>
     </row>
     <row r="682">
@@ -42081,7 +42081,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="683">
@@ -42142,7 +42142,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>2895.69</v>
+        <v>2914.21</v>
       </c>
     </row>
     <row r="684">
@@ -42203,7 +42203,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>12251</v>
+        <v>12329.35</v>
       </c>
     </row>
     <row r="685">
@@ -42264,7 +42264,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>13364.72</v>
+        <v>13450.2</v>
       </c>
     </row>
     <row r="686">
@@ -42325,7 +42325,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>14478.45</v>
+        <v>14571.05</v>
       </c>
     </row>
     <row r="687">
@@ -42386,7 +42386,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>66823.61</v>
+        <v>67251</v>
       </c>
     </row>
     <row r="688">
@@ -42447,7 +42447,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>8575.700000000001</v>
+        <v>8630.549999999999</v>
       </c>
     </row>
     <row r="689">
@@ -42508,7 +42508,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>2784.32</v>
+        <v>2802.13</v>
       </c>
     </row>
     <row r="690">
@@ -42569,7 +42569,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2338.83</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="691">
@@ -42630,7 +42630,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>33411.81</v>
+        <v>33625.5</v>
       </c>
     </row>
     <row r="692">
@@ -42691,7 +42691,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>2338.83</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="693">
@@ -42752,7 +42752,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>4343.53</v>
+        <v>4371.32</v>
       </c>
     </row>
     <row r="694">
@@ -42813,7 +42813,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2784.32</v>
+        <v>2802.13</v>
       </c>
     </row>
     <row r="695">
@@ -42874,7 +42874,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="696">
@@ -42935,7 +42935,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>11137.27</v>
+        <v>11208.5</v>
       </c>
     </row>
     <row r="697">
@@ -42996,7 +42996,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>22274.54</v>
+        <v>22417</v>
       </c>
     </row>
     <row r="698">
@@ -43057,7 +43057,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>11137.27</v>
+        <v>11208.5</v>
       </c>
     </row>
     <row r="699">
@@ -43118,7 +43118,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>33413.34</v>
+        <v>33627.04</v>
       </c>
     </row>
     <row r="700">
@@ -43179,7 +43179,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3341.18</v>
+        <v>3362.55</v>
       </c>
     </row>
     <row r="701">
@@ -43240,7 +43240,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>18933.36</v>
+        <v>18992.93</v>
       </c>
     </row>
     <row r="702">
@@ -43301,7 +43301,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>66823.61</v>
+        <v>67033.86</v>
       </c>
     </row>
     <row r="703">
@@ -43362,7 +43362,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>36752.99</v>
+        <v>36868.62</v>
       </c>
     </row>
     <row r="704">
@@ -43423,7 +43423,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2353.3</v>
+        <v>2360.71</v>
       </c>
     </row>
     <row r="705">
@@ -43484,7 +43484,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2784.32</v>
+        <v>2793.08</v>
       </c>
     </row>
     <row r="706">
@@ -43545,7 +43545,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>13364.72</v>
+        <v>13406.77</v>
       </c>
     </row>
     <row r="707">
@@ -43606,7 +43606,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>2338.83</v>
+        <v>2346.19</v>
       </c>
     </row>
     <row r="708">
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>38980.44</v>
+        <v>39103.09</v>
       </c>
     </row>
     <row r="709">
@@ -43728,7 +43728,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3898.04</v>
+        <v>3910.31</v>
       </c>
     </row>
     <row r="710">
@@ -43789,7 +43789,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>33411.81</v>
+        <v>33516.93</v>
       </c>
     </row>
     <row r="711">
@@ -43850,7 +43850,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="712">
@@ -43911,7 +43911,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>9287.370000000001</v>
+        <v>9316.59</v>
       </c>
     </row>
     <row r="713">
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>11137.27</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="714">
@@ -44033,7 +44033,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>11137.27</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="715">
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>5568.63</v>
+        <v>5586.16</v>
       </c>
     </row>
     <row r="716">
@@ -44155,7 +44155,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>7796.09</v>
+        <v>7820.62</v>
       </c>
     </row>
     <row r="717">
@@ -44216,7 +44216,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>28373.31</v>
+        <v>28462.58</v>
       </c>
     </row>
     <row r="718">
@@ -44277,7 +44277,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="719">
@@ -44338,7 +44338,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="720">
@@ -44399,7 +44399,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>8909.82</v>
+        <v>8937.85</v>
       </c>
     </row>
     <row r="721">
@@ -44460,7 +44460,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>16705.9</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="722">
@@ -44521,7 +44521,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>22274.54</v>
+        <v>22344.62</v>
       </c>
     </row>
     <row r="723">
@@ -44582,7 +44582,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>3118.44</v>
+        <v>3128.25</v>
       </c>
     </row>
     <row r="724">
@@ -44643,7 +44643,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>44549.08</v>
+        <v>44689.24</v>
       </c>
     </row>
     <row r="725">
@@ -44704,7 +44704,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>4454.91</v>
+        <v>4468.92</v>
       </c>
     </row>
     <row r="726">
@@ -44765,7 +44765,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>3136.36</v>
+        <v>3146.22</v>
       </c>
     </row>
     <row r="727">
@@ -44826,7 +44826,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>5522.57</v>
+        <v>5539.95</v>
       </c>
     </row>
     <row r="728">
@@ -44887,7 +44887,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>44549.08</v>
+        <v>44689.24</v>
       </c>
     </row>
     <row r="729">
@@ -44948,7 +44948,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>7796.09</v>
+        <v>7820.62</v>
       </c>
     </row>
     <row r="730">
@@ -45009,7 +45009,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>4454.91</v>
+        <v>4468.92</v>
       </c>
     </row>
     <row r="731">
@@ -45070,7 +45070,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>5568.63</v>
+        <v>5586.16</v>
       </c>
     </row>
     <row r="732">
@@ -45131,7 +45131,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="733">
@@ -45192,7 +45192,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>15592.18</v>
+        <v>15641.23</v>
       </c>
     </row>
     <row r="734">
@@ -45253,7 +45253,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>4454.91</v>
+        <v>4468.92</v>
       </c>
     </row>
     <row r="735">
@@ -45314,7 +45314,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>13810.21</v>
+        <v>13853.67</v>
       </c>
     </row>
     <row r="736">
@@ -45375,7 +45375,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>8107.93</v>
+        <v>8133.44</v>
       </c>
     </row>
     <row r="737">
@@ -45436,7 +45436,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>6682.36</v>
+        <v>6703.39</v>
       </c>
     </row>
     <row r="738">
@@ -45497,7 +45497,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>11137.27</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="739">
@@ -45558,7 +45558,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>2338.83</v>
+        <v>2346.19</v>
       </c>
     </row>
     <row r="740">
@@ -45619,7 +45619,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>2338.83</v>
+        <v>2346.19</v>
       </c>
     </row>
     <row r="741">
@@ -45680,7 +45680,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>16705.9</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="742">
@@ -45741,7 +45741,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>37866.71</v>
+        <v>37985.86</v>
       </c>
     </row>
     <row r="743">
@@ -45802,7 +45802,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>11137.27</v>
+        <v>11172.31</v>
       </c>
     </row>
     <row r="744">
@@ -45863,7 +45863,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>10023.54</v>
+        <v>10055.08</v>
       </c>
     </row>
     <row r="745">
@@ -45924,7 +45924,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>4454.91</v>
+        <v>4468.92</v>
       </c>
     </row>
     <row r="746">
@@ -45985,7 +45985,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3730.99</v>
+        <v>3742.72</v>
       </c>
     </row>
     <row r="747">
@@ -46046,7 +46046,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>7633.46</v>
+        <v>7665.1</v>
       </c>
     </row>
     <row r="748">
@@ -46107,7 +46107,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>13753.06</v>
+        <v>13810.06</v>
       </c>
     </row>
     <row r="749">
@@ -46168,7 +46168,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.4</v>
       </c>
     </row>
     <row r="750">
@@ -46229,7 +46229,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.03</v>
       </c>
     </row>
     <row r="751">
@@ -46290,7 +46290,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>6682.36</v>
+        <v>6710.06</v>
       </c>
     </row>
     <row r="752">
@@ -46351,7 +46351,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.37</v>
       </c>
     </row>
     <row r="753">
@@ -46412,7 +46412,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>2394.51</v>
+        <v>2404.44</v>
       </c>
     </row>
     <row r="754">
@@ -46473,7 +46473,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>6682.36</v>
+        <v>6710.06</v>
       </c>
     </row>
     <row r="755">
@@ -46534,7 +46534,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>2450.2</v>
+        <v>2460.35</v>
       </c>
     </row>
     <row r="756">
@@ -46595,7 +46595,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="757">
@@ -46656,7 +46656,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.03</v>
       </c>
     </row>
     <row r="758">
@@ -46717,7 +46717,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>6682.36</v>
+        <v>6710.06</v>
       </c>
     </row>
     <row r="759">
@@ -46778,7 +46778,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>3653.02</v>
+        <v>3668.17</v>
       </c>
     </row>
     <row r="760">
@@ -46839,7 +46839,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2338.83</v>
+        <v>2348.52</v>
       </c>
     </row>
     <row r="761">
@@ -46900,7 +46900,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>3058.02</v>
+        <v>3070.69</v>
       </c>
     </row>
     <row r="762">
@@ -46961,7 +46961,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>11752.6</v>
+        <v>11801.32</v>
       </c>
     </row>
     <row r="763">
@@ -47022,7 +47022,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>8171.97</v>
+        <v>8205.84</v>
       </c>
     </row>
     <row r="764">
@@ -47083,7 +47083,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>7555.24</v>
+        <v>7586.56</v>
       </c>
     </row>
     <row r="765">
@@ -47144,7 +47144,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.37</v>
       </c>
     </row>
     <row r="766">
@@ -47205,7 +47205,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>2784.32</v>
+        <v>2795.86</v>
       </c>
     </row>
     <row r="767">
@@ -47266,7 +47266,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="768">
@@ -47327,7 +47327,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>2450.2</v>
+        <v>2460.35</v>
       </c>
     </row>
     <row r="769">
@@ -47388,7 +47388,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>3808.95</v>
+        <v>3824.73</v>
       </c>
     </row>
     <row r="770">
@@ -47449,7 +47449,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>10023.54</v>
+        <v>10065.09</v>
       </c>
     </row>
     <row r="771">
@@ -47510,7 +47510,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>2444.68</v>
+        <v>2454.81</v>
       </c>
     </row>
     <row r="772">
@@ -47571,7 +47571,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.03</v>
       </c>
     </row>
     <row r="773">
@@ -47632,7 +47632,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>13364.72</v>
+        <v>13420.12</v>
       </c>
     </row>
     <row r="774">
@@ -47693,7 +47693,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.37</v>
       </c>
     </row>
     <row r="775">
@@ -47754,7 +47754,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.03</v>
       </c>
     </row>
     <row r="776">
@@ -47815,7 +47815,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>17819.63</v>
+        <v>17893.49</v>
       </c>
     </row>
     <row r="777">
@@ -47876,7 +47876,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>2784.32</v>
+        <v>2795.86</v>
       </c>
     </row>
     <row r="778">
@@ -47937,7 +47937,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="779">
@@ -47998,7 +47998,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="780">
@@ -48059,7 +48059,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="781">
@@ -48120,7 +48120,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>5457.26</v>
+        <v>5479.88</v>
       </c>
     </row>
     <row r="782">
@@ -48181,7 +48181,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>14478.45</v>
+        <v>14538.46</v>
       </c>
     </row>
     <row r="783">
@@ -48242,7 +48242,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>4009.42</v>
+        <v>4026.04</v>
       </c>
     </row>
     <row r="784">
@@ -48303,7 +48303,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.4</v>
       </c>
     </row>
     <row r="785">
@@ -48364,7 +48364,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>2358.47</v>
+        <v>2368.25</v>
       </c>
     </row>
     <row r="786">
@@ -48425,7 +48425,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>11137.27</v>
+        <v>11183.43</v>
       </c>
     </row>
     <row r="787">
@@ -48486,7 +48486,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>17262.77</v>
+        <v>17334.32</v>
       </c>
     </row>
     <row r="788">
@@ -48547,7 +48547,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>22274.54</v>
+        <v>22366.86</v>
       </c>
     </row>
     <row r="789">
@@ -48608,7 +48608,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>10580.41</v>
+        <v>10624.26</v>
       </c>
     </row>
     <row r="790">
@@ -48669,7 +48669,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.4</v>
       </c>
     </row>
     <row r="791">
@@ -48730,7 +48730,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>44549.08</v>
+        <v>44733.72</v>
       </c>
     </row>
     <row r="792">
@@ -48791,7 +48791,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="793">
@@ -48852,7 +48852,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="794">
@@ -48913,7 +48913,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="795">
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>22274.54</v>
+        <v>22320.68</v>
       </c>
     </row>
     <row r="796">
@@ -49035,7 +49035,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>2405.65</v>
+        <v>2410.63</v>
       </c>
     </row>
     <row r="797">
@@ -49096,7 +49096,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="798">
@@ -49157,7 +49157,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>4009.42</v>
+        <v>4017.72</v>
       </c>
     </row>
     <row r="799">
@@ -49218,7 +49218,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>5442.1</v>
+        <v>5453.37</v>
       </c>
     </row>
     <row r="800">
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>7796.09</v>
+        <v>7812.24</v>
       </c>
     </row>
     <row r="801">
@@ -49340,7 +49340,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="802">
@@ -49401,7 +49401,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="803">
@@ -49462,7 +49462,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>10023.54</v>
+        <v>10044.31</v>
       </c>
     </row>
     <row r="804">
@@ -49523,7 +49523,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>5568.63</v>
+        <v>5580.17</v>
       </c>
     </row>
     <row r="805">
@@ -49584,7 +49584,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>22274.54</v>
+        <v>22320.68</v>
       </c>
     </row>
     <row r="806">
@@ -49645,7 +49645,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>4454.91</v>
+        <v>4464.14</v>
       </c>
     </row>
     <row r="807">
@@ -49706,7 +49706,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>7796.09</v>
+        <v>7812.24</v>
       </c>
     </row>
     <row r="808">
@@ -49767,7 +49767,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>35639.26</v>
+        <v>35713.09</v>
       </c>
     </row>
     <row r="809">
@@ -49828,7 +49828,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>18885.47</v>
+        <v>18924.59</v>
       </c>
     </row>
     <row r="810">
@@ -49889,7 +49889,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>4454.91</v>
+        <v>4464.14</v>
       </c>
     </row>
     <row r="811">
@@ -49950,7 +49950,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>45340.38</v>
+        <v>45434.3</v>
       </c>
     </row>
     <row r="812">
@@ -50011,7 +50011,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>10023.54</v>
+        <v>10044.31</v>
       </c>
     </row>
     <row r="813">
@@ -50072,7 +50072,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>2895.69</v>
+        <v>2901.69</v>
       </c>
     </row>
     <row r="814">
@@ -50133,7 +50133,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2784.32</v>
+        <v>2790.09</v>
       </c>
     </row>
     <row r="815">
@@ -50194,7 +50194,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8370.26</v>
       </c>
     </row>
     <row r="816">
@@ -50255,7 +50255,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>3247.21</v>
+        <v>3253.94</v>
       </c>
     </row>
     <row r="817">
@@ -50316,7 +50316,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>4109.65</v>
+        <v>4118.17</v>
       </c>
     </row>
     <row r="818">
@@ -50377,7 +50377,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="819">
@@ -50438,7 +50438,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>11137.27</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="820">
@@ -50499,7 +50499,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>3563.93</v>
+        <v>3571.31</v>
       </c>
     </row>
     <row r="821">
@@ -50560,7 +50560,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>33411.81</v>
+        <v>33481.02</v>
       </c>
     </row>
     <row r="822">
@@ -50621,7 +50621,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>11025.9</v>
+        <v>11048.74</v>
       </c>
     </row>
     <row r="823">
@@ -50682,7 +50682,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>15592.18</v>
+        <v>15624.48</v>
       </c>
     </row>
     <row r="824">
@@ -50743,7 +50743,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>22274.54</v>
+        <v>22320.68</v>
       </c>
     </row>
     <row r="825">
@@ -50804,7 +50804,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>2784.32</v>
+        <v>2790.09</v>
       </c>
     </row>
     <row r="826">
@@ -50865,7 +50865,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="827">
@@ -50926,7 +50926,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="828">
@@ -50987,7 +50987,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>4454.91</v>
+        <v>4464.14</v>
       </c>
     </row>
     <row r="829">
@@ -51048,7 +51048,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="830">
@@ -51113,7 +51113,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>191168.9</v>
+        <v>191564.92</v>
       </c>
     </row>
     <row r="831">
@@ -51174,7 +51174,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>16705.9</v>
+        <v>16740.51</v>
       </c>
     </row>
     <row r="832">
@@ -51235,7 +51235,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>15035.31</v>
+        <v>15066.46</v>
       </c>
     </row>
     <row r="833">
@@ -51296,7 +51296,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="834">
@@ -51357,7 +51357,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>5568.63</v>
+        <v>5580.17</v>
       </c>
     </row>
     <row r="835">
@@ -51418,7 +51418,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="836">
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="837">
@@ -51540,7 +51540,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="838">
@@ -51601,7 +51601,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>21606.3</v>
+        <v>21651.06</v>
       </c>
     </row>
     <row r="839">
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>18376.48</v>
+        <v>18297.54</v>
       </c>
     </row>
     <row r="840">
@@ -51723,7 +51723,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>38813.38</v>
+        <v>38646.65</v>
       </c>
     </row>
     <row r="841">
@@ -51784,7 +51784,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="842">
@@ -51845,7 +51845,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>59138.9</v>
+        <v>58884.85</v>
       </c>
     </row>
     <row r="843">
@@ -51906,7 +51906,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>10023.54</v>
+        <v>9980.48</v>
       </c>
     </row>
     <row r="844">
@@ -51967,7 +51967,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>7116.98</v>
+        <v>7086.41</v>
       </c>
     </row>
     <row r="845">
@@ -52028,7 +52028,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>5345.89</v>
+        <v>5322.92</v>
       </c>
     </row>
     <row r="846">
@@ -52089,7 +52089,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>7796.09</v>
+        <v>7762.6</v>
       </c>
     </row>
     <row r="847">
@@ -52150,7 +52150,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>3976</v>
+        <v>3958.92</v>
       </c>
     </row>
     <row r="848">
@@ -52211,7 +52211,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>7547.42</v>
+        <v>7515</v>
       </c>
     </row>
     <row r="849">
@@ -52272,7 +52272,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="850">
@@ -52333,7 +52333,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>11137.27</v>
+        <v>11089.43</v>
       </c>
     </row>
     <row r="851">
@@ -52394,7 +52394,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>2338.83</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="852">
@@ -52455,7 +52455,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>33411.81</v>
+        <v>33268.28</v>
       </c>
     </row>
     <row r="853">
@@ -52516,7 +52516,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>5011.77</v>
+        <v>4990.24</v>
       </c>
     </row>
     <row r="854">
@@ -52577,7 +52577,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>5123.14</v>
+        <v>5101.14</v>
       </c>
     </row>
     <row r="855">
@@ -52638,7 +52638,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="856">
@@ -52699,7 +52699,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>5011.77</v>
+        <v>4990.24</v>
       </c>
     </row>
     <row r="857">
@@ -52760,7 +52760,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>27843.17</v>
+        <v>27723.56</v>
       </c>
     </row>
     <row r="858">
@@ -52821,7 +52821,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>2784.32</v>
+        <v>2772.36</v>
       </c>
     </row>
     <row r="859">
@@ -52882,7 +52882,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="860">
@@ -52943,7 +52943,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>2338.83</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="861">
@@ -53004,7 +53004,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="862">
@@ -53065,7 +53065,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>2335.12</v>
+        <v>2325.09</v>
       </c>
     </row>
     <row r="863">
@@ -53126,7 +53126,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>3898.04</v>
+        <v>3881.3</v>
       </c>
     </row>
     <row r="864">
@@ -53187,7 +53187,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="865">
@@ -53248,7 +53248,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>9058.84</v>
+        <v>9019.93</v>
       </c>
     </row>
     <row r="866">
@@ -53309,7 +53309,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>22273.81</v>
+        <v>22178.13</v>
       </c>
     </row>
     <row r="867">
@@ -53370,7 +53370,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>6682.36</v>
+        <v>6653.66</v>
       </c>
     </row>
     <row r="868">
@@ -53431,7 +53431,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="869">
@@ -53492,7 +53492,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>27843.17</v>
+        <v>27723.56</v>
       </c>
     </row>
     <row r="870">
@@ -53553,7 +53553,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>18116.56</v>
+        <v>18038.73</v>
       </c>
     </row>
     <row r="871">
@@ -53614,7 +53614,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>4454.91</v>
+        <v>4435.77</v>
       </c>
     </row>
     <row r="872">
@@ -53675,7 +53675,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="873">
@@ -53736,7 +53736,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>2361.1</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="874">
@@ -53797,7 +53797,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="875">
@@ -53858,7 +53858,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>10023.54</v>
+        <v>9980.48</v>
       </c>
     </row>
     <row r="876">
@@ -53919,7 +53919,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>2358.47</v>
+        <v>2348.34</v>
       </c>
     </row>
     <row r="877">
@@ -53980,7 +53980,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="878">
@@ -54041,7 +54041,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>9010.049999999999</v>
+        <v>8971.34</v>
       </c>
     </row>
     <row r="879">
@@ -54102,7 +54102,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="880">
@@ -54163,7 +54163,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>7389.41</v>
+        <v>7357.67</v>
       </c>
     </row>
     <row r="881">
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>22274.54</v>
+        <v>22178.85</v>
       </c>
     </row>
     <row r="882">
@@ -54285,7 +54285,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>4454.91</v>
+        <v>4435.77</v>
       </c>
     </row>
     <row r="883">
@@ -54346,7 +54346,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>8909.82</v>
+        <v>8871.540000000001</v>
       </c>
     </row>
     <row r="884">
@@ -54407,7 +54407,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="885">
@@ -54468,7 +54468,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>2338.83</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="886">
@@ -54529,7 +54529,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>7457.54</v>
+        <v>7425.5</v>
       </c>
     </row>
     <row r="887">
@@ -54590,7 +54590,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>16705.9</v>
+        <v>16634.14</v>
       </c>
     </row>
     <row r="888">
@@ -54651,7 +54651,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>5433.87</v>
+        <v>5410.53</v>
       </c>
     </row>
     <row r="889">
@@ -54712,7 +54712,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="890">
@@ -54773,7 +54773,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>2338.83</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="891">
@@ -54834,7 +54834,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>5568.63</v>
+        <v>5544.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22292,7 +22292,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -24294,7 +24294,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25392,7 +25392,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -27039,7 +27039,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -28076,7 +28076,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28625,7 +28625,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28686,7 +28686,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -29544,7 +29544,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29910,7 +29910,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29925,7 +29925,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -30036,7 +30036,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30219,7 +30219,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30646,7 +30646,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30707,7 +30707,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30829,7 +30829,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31195,7 +31195,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31256,7 +31256,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31988,7 +31988,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32110,7 +32110,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32293,7 +32293,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32598,7 +32598,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34184,7 +34184,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34245,7 +34245,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34428,7 +34428,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34855,7 +34855,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -35221,7 +35221,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35404,7 +35404,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35663,7 +35663,7 @@
       </c>
       <c r="K577" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -36094,7 +36094,7 @@
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
@@ -36571,7 +36571,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39865,7 +39865,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40048,7 +40048,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -41024,7 +41024,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41512,7 +41512,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41817,7 +41817,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -42244,7 +42244,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42366,7 +42366,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42427,7 +42427,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42549,7 +42549,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42671,7 +42671,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42732,7 +42732,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42976,7 +42976,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43952,7 +43952,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44379,7 +44379,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44745,7 +44745,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44867,7 +44867,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44928,7 +44928,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45172,7 +45172,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45416,7 +45416,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45904,7 +45904,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46209,7 +46209,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48283,7 +48283,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48405,7 +48405,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -49198,7 +49198,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -49503,7 +49503,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -50052,7 +50052,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50235,7 +50235,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -50296,7 +50296,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -50418,7 +50418,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -50662,7 +50662,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -50723,7 +50723,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -50784,7 +50784,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -50906,7 +50906,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -51089,7 +51089,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -51104,7 +51104,7 @@
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
@@ -51337,7 +51337,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51947,7 +51947,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -52191,7 +52191,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52374,7 +52374,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -52435,7 +52435,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -52679,7 +52679,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -52984,7 +52984,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53899,7 +53899,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -54082,7 +54082,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -54143,7 +54143,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -54387,7 +54387,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -54448,7 +54448,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -54509,7 +54509,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54753,7 +54753,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/abr-2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LLANQUIHUE-DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN-SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Punta Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Departamento de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20198,12 +20198,12 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20320,12 +20320,12 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23557,7 +23557,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -25209,7 +25209,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25448,7 +25448,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27339,12 +27339,12 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27888,12 +27888,12 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29844,7 +29844,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -30519,7 +30519,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31800,7 +31800,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -32349,7 +32349,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -33447,7 +33447,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -33935,7 +33935,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34606,7 +34606,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -34667,7 +34667,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -35399,7 +35399,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35643,7 +35643,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35830,7 +35830,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -36013,7 +36013,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -36383,7 +36383,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37481,7 +37481,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -38152,7 +38152,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>MINEDUC ADMINISTRACION VIII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE PETORCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38518,7 +38518,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -38579,7 +38579,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -39006,7 +39006,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Palena</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39189,7 +39189,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39433,7 +39433,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -39555,7 +39555,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>SERPLAC II REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40460,7 +40460,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -42244,7 +42244,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42666,7 +42666,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -42727,7 +42727,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -42854,7 +42854,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43032,7 +43032,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -43642,7 +43642,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -44135,7 +44135,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44984,7 +44984,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -45106,7 +45106,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corporacion Municipal de Deportes y Recreación de </t>
+          <t>Corporacion Municipal de Deportes y Recreación de la comuna de San Pedro de Atacama</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -45167,7 +45167,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45594,7 +45594,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -46143,7 +46143,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -46204,7 +46204,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Salud</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -46631,7 +46631,7 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -47119,7 +47119,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -47180,7 +47180,7 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -47241,7 +47241,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -47424,7 +47424,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -47851,7 +47851,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -48278,7 +48278,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -48827,7 +48827,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -49376,7 +49376,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -49437,7 +49437,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -49559,7 +49559,7 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -49620,7 +49620,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
@@ -49681,7 +49681,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -49742,7 +49742,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -49864,7 +49864,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
@@ -50169,7 +50169,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -50281,7 +50281,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
@@ -50840,7 +50840,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
@@ -50906,7 +50906,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -50962,7 +50962,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -51515,7 +51515,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -52369,7 +52369,7 @@
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -52918,7 +52918,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -52979,7 +52979,7 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -53350,7 +53350,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -53467,7 +53467,7 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -54204,7 +54204,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -54260,7 +54260,7 @@
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -54382,7 +54382,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
